--- a/Configs/GameConfig/Datas/fg/#Quest-任务.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Quest-任务.xlsx
@@ -698,12 +698,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>出现时机:start=开局/territory_visible=领地在地图上可见(按幕或亲自探索到)/prereq=前置任务完成/side_found=发现支线地点</t>
+          <t>出现时机:start=开局/territory_visible=领地在地图上可见(按幕或亲自探索到)/prereq=前置任务完成/side_found=发现支线地点/pace=第一幕节奏点到达(前置列写节奏点ID,fg.TbActPacing)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>前置任务ID(fg.TbQuest.id;none=没有)</t>
+          <t>前置任务ID(fg.TbQuest.id;出现时机 pace 时写节奏点ID;none=没有)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>pace</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>belts_open</t>
         </is>
       </c>
       <c r="N10" t="n">

--- a/Configs/GameConfig/Datas/fg/#Quest-任务.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Quest-任务.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>地图位置:none/core=归还核心/territory_center=领地中心/side_site=发现的支线地点/side_nearest=领地里离核心最近的支线地点/side_center=领地里离中心最近的支线地点</t>
+          <t>地图位置:none/core=归还核心/territory_center=领地中心/side_site=发现的支线地点/side_nearest=领地里离核心最近的支线地点/side_center=领地里离中心最近的支线地点/belt_outer=领地外圈危害带外缘朝核心一侧(往外 hazard.acid_marsh.pickup_margin 格;不进危害带)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>side_nearest</t>
+          <t>belt_outer</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
